--- a/artfynd/A 51110-2025 artfynd.xlsx
+++ b/artfynd/A 51110-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96196422</v>
+        <v>97924301</v>
       </c>
       <c r="B2" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kråkmossen V, Sm</t>
+          <t>Kråkmossen, Runtorp 1:4, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555034.1273575997</v>
+        <v>555246</v>
       </c>
       <c r="R2" t="n">
-        <v>6272120.706708802</v>
+        <v>6272166</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,22 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-01-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-01-05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>A74213-2021</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96196447</v>
+        <v>96196422</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555060.0556674351</v>
+        <v>555034</v>
       </c>
       <c r="R3" t="n">
-        <v>6272121.045332938</v>
+        <v>6272120</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,19 +853,9 @@
           <t>2021-09-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,59 +883,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97923941</v>
+        <v>97924213</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kråkmossen, Runtorp 1:4, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555075.0225905949</v>
+        <v>555065</v>
       </c>
       <c r="R4" t="n">
-        <v>6272115.734518243</v>
+        <v>6272148</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,21 +954,11 @@
           <t>2022-01-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-01-05</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>A74213-2021</t>
@@ -1017,8 +970,24 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1035,59 +1004,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97923939</v>
+        <v>97924318</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kråkmossen, Runtorp 1:4, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555087.1016989573</v>
+        <v>555088</v>
       </c>
       <c r="R5" t="n">
-        <v>6272120.29745393</v>
+        <v>6272147</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,24 +1084,9 @@
           <t>2022-01-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-01-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>A74213-2021</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,59 +1113,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97923934</v>
+        <v>99589144</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kråkmossen, Runtorp 1:4, Sm</t>
+          <t>Runtorp, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555066.3160301348</v>
+        <v>555151</v>
       </c>
       <c r="R6" t="n">
-        <v>6272148.658786662</v>
+        <v>6272105</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,27 +1187,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-01-05</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-01-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>A74213-2021</t>
+          <t>2022-03-31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,6 +1201,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1287,59 +1220,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97923944</v>
+        <v>99589160</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5495</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>101410</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kråkmossen, Runtorp 1:4, Sm</t>
+          <t>Runtorp, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555059.0314430492</v>
+        <v>555210</v>
       </c>
       <c r="R7" t="n">
-        <v>6272114.974962434</v>
+        <v>6272120</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,27 +1294,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-01-05</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-01-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>A74213-2021</t>
+          <t>2022-03-31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,6 +1308,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1413,15 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97924318</v>
+        <v>97924320</v>
       </c>
       <c r="B8" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1465,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555087.3007924911</v>
+        <v>555088</v>
       </c>
       <c r="R8" t="n">
-        <v>6272147.281103272</v>
+        <v>6272147</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1498,19 +1407,9 @@
           <t>2022-01-05</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-01-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1537,62 +1436,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97923935</v>
+        <v>102200640</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kråkmossen, Runtorp 1:4, Sm</t>
+          <t>Runtorp, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555075.7950070467</v>
+        <v>555052</v>
       </c>
       <c r="R9" t="n">
-        <v>6272141.073787612</v>
+        <v>6272108</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1616,27 +1512,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-01-05</t>
+          <t>2022-07-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-01-05</t>
+          <t>2022-07-11</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>A74213-2021</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1663,15 +1554,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97923936</v>
+        <v>96196447</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,26 +1582,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kråkmossen, Runtorp 1:4, Sm</t>
+          <t>Kråkmossen V, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555076.8120063443</v>
+        <v>555060</v>
       </c>
       <c r="R10" t="n">
-        <v>6272147.694663127</v>
+        <v>6272121</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1742,27 +1623,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-01-05</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-01-05</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>A74213-2021</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1771,6 +1637,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1789,15 +1656,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97923942</v>
+        <v>97923934</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,7 +1686,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1838,10 +1700,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555076.7567245219</v>
+        <v>555067</v>
       </c>
       <c r="R11" t="n">
-        <v>6272109.700178421</v>
+        <v>6272149</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1871,19 +1733,9 @@
           <t>2022-01-05</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-01-05</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1915,15 +1767,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97923940</v>
+        <v>97923935</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1950,7 +1797,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1964,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555083.9499885914</v>
+        <v>555076</v>
       </c>
       <c r="R12" t="n">
-        <v>6272108.142268473</v>
+        <v>6272141</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1997,19 +1844,9 @@
           <t>2022-01-05</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-01-05</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2041,15 +1878,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>97923945</v>
+        <v>97923936</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,10 +1922,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555048.0771961162</v>
+        <v>555076</v>
       </c>
       <c r="R13" t="n">
-        <v>6272108.774883832</v>
+        <v>6272148</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2123,19 +1955,9 @@
           <t>2022-01-05</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-01-05</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2167,62 +1989,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>97924320</v>
+        <v>97923937</v>
       </c>
       <c r="B14" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kråkmossen, Runtorp 1:4, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555087.3007924911</v>
+        <v>555080</v>
       </c>
       <c r="R14" t="n">
-        <v>6272147.281103272</v>
+        <v>6272152</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2252,19 +2066,14 @@
           <t>2022-01-05</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-01-05</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>A74213-2021</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2291,15 +2100,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>97923937</v>
+        <v>97923938</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2326,7 +2130,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2340,10 +2144,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555080.6160892283</v>
+        <v>555088</v>
       </c>
       <c r="R15" t="n">
-        <v>6272152.149425415</v>
+        <v>6272147</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2373,19 +2177,9 @@
           <t>2022-01-05</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-01-05</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2417,53 +2211,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>97924301</v>
+        <v>97923939</v>
       </c>
       <c r="B16" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kråkmossen, Runtorp 1:4, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555246.5148172412</v>
+        <v>555087</v>
       </c>
       <c r="R16" t="n">
-        <v>6272165.88392154</v>
+        <v>6272120</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2493,21 +2288,11 @@
           <t>2022-01-05</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-01-05</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
           <t>A74213-2021</t>
@@ -2519,7 +2304,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2538,53 +2322,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>97924213</v>
+        <v>97923940</v>
       </c>
       <c r="B17" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kråkmossen, Runtorp 1:4, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555065.7715601271</v>
+        <v>555084</v>
       </c>
       <c r="R17" t="n">
-        <v>6272148.101041729</v>
+        <v>6272108</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2614,21 +2399,11 @@
           <t>2022-01-05</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-01-05</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
           <t>A74213-2021</t>
@@ -2640,24 +2415,8 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2674,15 +2433,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>97923938</v>
+        <v>97923941</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2709,7 +2463,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2723,10 +2477,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555087.3007924911</v>
+        <v>555075</v>
       </c>
       <c r="R18" t="n">
-        <v>6272147.281103272</v>
+        <v>6272116</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2756,19 +2510,9 @@
           <t>2022-01-05</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-01-05</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2800,15 +2544,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>97923943</v>
+        <v>97923942</v>
       </c>
       <c r="B19" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2835,7 +2574,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2849,10 +2588,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555071.2328547564</v>
+        <v>555077</v>
       </c>
       <c r="R19" t="n">
-        <v>6272110.178638271</v>
+        <v>6272110</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2882,19 +2621,9 @@
           <t>2022-01-05</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-01-05</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2926,15 +2655,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>99588946</v>
+        <v>97923943</v>
       </c>
       <c r="B20" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2961,7 +2685,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2969,19 +2693,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Runtorp, Sm</t>
+          <t>Kråkmossen, Runtorp 1:4, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555107.004871806</v>
+        <v>555071</v>
       </c>
       <c r="R20" t="n">
-        <v>6272117.25381174</v>
+        <v>6272110</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3008,22 +2729,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-03-31</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-01-05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-03-31</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-01-05</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>A74213-2021</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3032,7 +2748,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3051,64 +2766,57 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>102200640</v>
+        <v>97923944</v>
       </c>
       <c r="B21" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Runtorp, Sm</t>
+          <t>Kråkmossen, Runtorp 1:4, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555051.9388703624</v>
+        <v>555059</v>
       </c>
       <c r="R21" t="n">
-        <v>6272108.825319823</v>
+        <v>6272115</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3132,22 +2840,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>20:25</t>
+          <t>2022-01-05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>20:25</t>
+          <t>2022-01-05</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>A74213-2021</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3171,6 +2874,328 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>97923945</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kråkmossen, Runtorp 1:4, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>555048</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6272109</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Mortorp</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2022-01-05</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2022-01-05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>A74213-2021</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>99588946</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Runtorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>555107</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6272117</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Mortorp</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-03-31</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-03-31</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>99589193</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Runtorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>555219</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6272137</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Mortorp</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2022-03-31</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2022-03-31</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51110-2025 artfynd.xlsx
+++ b/artfynd/A 51110-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97924301</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196422</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97924213</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97924318</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99589144</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99589160</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1433,6 +1468,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97924320</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1551,6 +1591,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102200640</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1653,6 +1698,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196447</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1764,6 +1814,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97923934</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1875,6 +1930,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97923935</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1986,6 +2046,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97923936</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2097,6 +2162,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97923937</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2208,6 +2278,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97923938</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2319,6 +2394,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97923939</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2430,6 +2510,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97923940</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2541,6 +2626,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97923941</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2652,6 +2742,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97923942</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2763,6 +2858,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97923943</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2874,6 +2974,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97923944</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2985,6 +3090,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97923945</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3095,6 +3205,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99588946</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3196,8 +3311,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99589193</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>